--- a/1-output/M3/gap-analysis-magdalena-2026-05-12.xlsx
+++ b/1-output/M3/gap-analysis-magdalena-2026-05-12.xlsx
@@ -140,10 +140,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fecha: 2026-05-12  ·  Commit HEAD: 37015cd</t>
+          <t>Fecha: 2026-05-12  ·  Commit HEAD: 7d61423</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -667,14 +667,14 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>94.0%</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -694,14 +694,14 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>92.1%</t>
         </is>
       </c>
     </row>
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>93.8%</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -775,14 +775,14 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -793,23 +793,23 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>29</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>96.7%</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -1088,24 +1088,24 @@
           <t>Revisar avisos de mantenimiento</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WorkRequests page filtros + audit log review</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -1135,24 +1135,24 @@
           <t>Obtener información del mantenimiento de todas las áreas involucradas en la tarea</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -1182,24 +1182,24 @@
           <t>Ejecución, abastecimiento, operaciones, etc.</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -1370,24 +1370,24 @@
           <t>Identificar oportunidades y brechas ocurridas en los procesos</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -1417,24 +1417,24 @@
           <t>Analizar el desempeño de la ejecución de mantenimiento</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PerformanceAnalysis page + variance_alerts + post-review + DE KPIs</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -1511,24 +1511,24 @@
           <t>Realizar reunión de desempeño</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Management review skill + dashboards consolidados + Reports module</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -1558,24 +1558,24 @@
           <t>Confeccionar lista de mejoras y plan de cierre</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>improvement_actions module + CAPA tracking + action items</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -1605,24 +1605,24 @@
           <t>Generar listado de acciones y/o estándares para la mejora continua</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>improvement_actions module + CAPA tracking + action items</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -1885,24 +1885,24 @@
           <t>¿Se puede completar el programa?</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="44" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -1932,24 +1932,24 @@
           <t>¿Se necesita tiempo adicional?</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -1979,24 +1979,24 @@
           <t>¿Tiempo adicional aprobado?</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -2026,24 +2026,24 @@
           <t>¿Se necesitan recursos adicionales?</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -2073,24 +2073,24 @@
           <t>¿Recursos adicionales aprobados?</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -2402,24 +2402,24 @@
           <t>¿Están todos los rercursos disponibles?</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -2449,24 +2449,24 @@
           <t>¿Se pueden obtener recursos y alcanzar resultados?</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -2496,24 +2496,24 @@
           <t>Obtener los recursos necesarios</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="44" customHeight="1">
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -2543,24 +2543,24 @@
           <t>¿Están correctas las condiciones del lugar de trabajo?</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>checklist pre-execution + SF-662 preparativos · UI completa pendiente</t>
+          <t>Pre-execution checklist + SF-662 preparativos + JRA</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -2590,24 +2590,24 @@
           <t>¿Se pueden establecer condiciones en el lugar de trabajo y alcanzar resultados?</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="1">
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -2637,24 +2637,24 @@
           <t>Establecer condiciones requeridas en el lugar de trabajo</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
@@ -2966,7 +2966,7 @@
           <t>¿Se requiere trabajo adicional?</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -3013,7 +3013,7 @@
           <t>¿Se puede completar el trabajo adicional y seguir cumpliendo los resultados?</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -3060,7 +3060,7 @@
           <t>Ejecutar trabajo adicional</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -3440,7 +3440,7 @@
           <t>Entregar formalmente equipo a operaciones</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -3487,7 +3487,7 @@
           <t>Devolver herramientas, repuestos y eliminar residuos</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -4456,7 +4456,7 @@
           <t>Sistema envia mail automático al creador del requerimiento y otro al aprobador solicitando su aprobación. Una vez que el trabajo es aprobado, el solicitante también recibe una notificación indicando que el trabajo fue aprobado</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -4503,24 +4503,24 @@
           <t>Revisión de requerimientos de trabajo (aprobación/rechazo)</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -4550,7 +4550,7 @@
           <t>Cerrar requerimiento duplicado</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -4644,24 +4644,24 @@
           <t>Descripción del Trabajo</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -4691,24 +4691,24 @@
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -4738,24 +4738,24 @@
           <t>¿Es necesario el trabajo?</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -4785,24 +4785,24 @@
           <t>¿Es adecuado el trabajo?</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -4832,7 +4832,7 @@
           <t>¿Esta disponible el presupuesto?</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -5045,24 +5045,24 @@
           <t>Vista de producción</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Production tab Executive dashboard</t>
         </is>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -5092,24 +5092,24 @@
           <t>Kpi producción</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Production tab Executive · usa proxies, falta data plant SCADA real</t>
+          <t>Production tab Executive con KPIs (proxies hasta integrar SCADA cliente)</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="44" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -5139,24 +5139,24 @@
           <t>Toneladas procesadas t/d, utilización %, rendimiento t/h, otros</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Production tab Executive · usa proxies, falta data plant SCADA real</t>
+          <t>Production tab Executive con KPIs (proxies hasta integrar SCADA cliente)</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
@@ -5186,24 +5186,24 @@
           <t>Vista de mantenimiento</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -5233,24 +5233,24 @@
           <t>Kpi resultados</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -5327,24 +5327,24 @@
           <t>Kpi Gastos de mantenimiento</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -5374,24 +5374,24 @@
           <t>Opex real vs plan (CeCo / Clase gasto)</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Costos tab por OT · agregado por CeCo pendiente</t>
+          <t>Costos tab por OT + Budget vs Actual KPI (agregado CeCo en Tanda 0E SP8)</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Tanda 0E</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -5421,24 +5421,24 @@
           <t>Capex real vs plan</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Costos tab por OT · agregado por CeCo pendiente</t>
+          <t>Costos tab por OT + Budget vs Actual KPI (agregado CeCo en Tanda 0E SP8)</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Tanda 0E</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -5468,24 +5468,24 @@
           <t>KPIs disciplina operacional</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
@@ -5562,24 +5562,24 @@
           <t>% Órdenes atrasadas</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -5703,24 +5703,24 @@
           <t>% Cumplimiento del plan matriz</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Reliability strategy + RCM + maintenance-strategy-drivers context</t>
+          <t>Reliability strategy + RCM + maintenance-strategy-drivers + 5y compliance</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -5844,24 +5844,24 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
@@ -5891,24 +5891,24 @@
           <t>Dotación de mantenimiento</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -5985,24 +5985,24 @@
           <t>% Dotación real vs nominal (staff)</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6032,24 +6032,24 @@
           <t>Vista de HSE</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HSE tab Executive con KPIs Critical Alerts (integraciones plant Q3-2026)</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -6058,7 +6058,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6079,24 +6079,24 @@
           <t>Accidentes con tiempo perdido (CTP)</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>HSE tab Executive · falta integración incidentes plant</t>
+          <t>HSE tab Executive con KPIs critical_alerts + dashboards (integración data plant Q3)</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6126,24 +6126,24 @@
           <t>Accidentes sin tiempo perdido (STP)</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>HSE tab Executive · falta integración incidentes plant</t>
+          <t>HSE tab Executive con KPIs critical_alerts + dashboards (integración data plant Q3)</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6173,24 +6173,24 @@
           <t>Otros índices</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HSE tab Executive con KPIs Critical Alerts (integraciones plant Q3-2026)</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -6199,7 +6199,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6220,24 +6220,24 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dashboard 'All' filtros con vista consolidada</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
@@ -6314,24 +6314,24 @@
           <t>Órdenes atrasadas</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Late Work Orders KPI + Cycle Times</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -6434,7 +6434,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
+    <row r="32" ht="48" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6455,24 +6455,24 @@
           <t>Cumplimiento del plan matriz</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Reliability strategy + RCM + maintenance-strategy-drivers context</t>
+          <t>Reliability strategy + RCM + maintenance-strategy-drivers + 5y compliance</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6549,24 +6549,24 @@
           <t>Trabajo planificado</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Planned Work KPI (% planned vs reactive)</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6643,24 +6643,24 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dashboard 'All' filtros con vista consolidada</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6690,24 +6690,24 @@
           <t>Planificación</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Planning KPIs engine (11 indicadores) + Scheduling KPIs</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
@@ -6810,7 +6810,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6831,24 +6831,24 @@
           <t>CONDITION BASED MAINTENANCE COST</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Costs card Executive Budget vs Actual</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -6904,7 +6904,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -6925,24 +6925,24 @@
           <t>CONTRACTOR COST</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>external_cost field + workforce contratistas + analytics</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="36" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7066,24 +7066,24 @@
           <t>STORES INVENTORY TURNS</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>InventoryItemModel + spare-parts optimizer + turn calc</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
+    <row r="46" ht="36" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7113,24 +7113,24 @@
           <t>Nivel de servicio (kpi de abastecimiento)</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -7139,7 +7139,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
+    <row r="47" ht="36" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7160,24 +7160,24 @@
           <t>Quiebre de stock (kpi de abastecimiento)</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
@@ -7186,7 +7186,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7207,24 +7207,24 @@
           <t>Confiabilidad</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reliability page MTBF/MTTR + Weibull + jackknife</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1">
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7254,24 +7254,24 @@
           <t>SYSTEMS COVERED BY CRITICALITY ANALYSIS</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>criticality_assessments + script seed_criticality covering full hierarchy</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
@@ -7468,7 +7468,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54" ht="36" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7489,24 +7489,24 @@
           <t>Ejecución</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Execution module + post_review + actual_hours tracking</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
@@ -7562,7 +7562,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
+    <row r="56" ht="32" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7583,118 +7583,118 @@
           <t>CONDITION BASED MAINTENANCE HOURS</t>
         </is>
       </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBM operations hours en task_type INSPECT/MONITOR</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="44" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>KPIS</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Nivel táctico &amp; operativo</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>REWORK</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>is_recurring flag + audit log · rework rate KPI dedicado pendiente</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>SP8</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
           <t>David</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>Nivel táctico &amp; operativo</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>REWORK</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>Por revisar con dev lead</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="I57" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>KPIS</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>Nivel táctico &amp; operativo</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>Detalle</t>
-        </is>
-      </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
           <t>MAINTENANCE TRAINING HOURS</t>
         </is>
       </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Training hours tracking no implementado (capacitación es módulo HR)</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>Q3-2026</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1">
+    <row r="60" ht="40" customHeight="1">
       <c r="A60" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7773,17 +7773,17 @@
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Pendiente verificar</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Workforce con specialty + categorization · ratio KPI pendiente</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>SP8</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -7797,7 +7797,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
+    <row r="61" ht="40" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -7818,24 +7818,24 @@
           <t>CRAFT WORKER ON SHIFT RATIO</t>
         </is>
       </c>
-      <c r="E61" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>shift_pattern + workforce on-shift detection (isTechOnShift)</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
@@ -7995,7 +7995,7 @@
           <t>Cerrar requerimiento duplicado</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8512,7 +8512,7 @@
           <t>Aprobación de ppto adicional</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8559,7 +8559,7 @@
           <t>Realizar análisis de riesgo para tareas críticas</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="44" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Planificación</t>
@@ -8653,24 +8653,24 @@
           <t>Asignar prioridad (aplicar estándar de priorización)</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>calculate-priority skill (R8 + GFSN) + SF-681 manual + priority_engine</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -8726,7 +8726,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Planificación</t>
@@ -8747,24 +8747,24 @@
           <t>Liberar orden de trabajo</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PUT /managed-work-orders/{id}/release endpoint + button UI</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
@@ -9300,7 +9300,7 @@
           <t>Coordinar con operaciones la entrega de equipos</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -9347,7 +9347,7 @@
           <t>Programar sólo tareas planificadas que cuenten con todos los repuestos y recursos en terreno</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10363,7 +10363,7 @@
           <t>Sistema envia mail automático al creador del requerimiento y otro al aprobador solicitando su aprobación. Una vez que el trabajo es aprobado, el solicitante también recibe una notificación indicando que el trabajo fue aprobado</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10410,24 +10410,24 @@
           <t>Revisión de requerimientos de trabajo (aprobación/rechazo)</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -10457,7 +10457,7 @@
           <t>Cerrar requerimiento duplicado</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -10551,24 +10551,24 @@
           <t>Descripción del Trabajo</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -10598,24 +10598,24 @@
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
@@ -10624,7 +10624,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -10645,24 +10645,24 @@
           <t>¿Es necesario el trabajo?</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Identificación</t>
@@ -10692,24 +10692,24 @@
           <t>¿Es adecuado el trabajo?</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WR approve/reject endpoints + WorkRequests page</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -10739,7 +10739,7 @@
           <t>¿Esta disponible el presupuesto?</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10938,7 +10938,7 @@
           <t>Cerrar requerimiento duplicado</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -11455,7 +11455,7 @@
           <t>Aprobación de ppto adicional</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -11502,7 +11502,7 @@
           <t>Realizar análisis de riesgo para tareas críticas</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
+    <row r="42" ht="44" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Planificación</t>
@@ -11596,24 +11596,24 @@
           <t>Asignar prioridad (aplicar estándar de priorización)</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>calculate-priority skill (R8 + GFSN) + SF-681 manual + priority_engine</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -11669,7 +11669,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
+    <row r="44" ht="36" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Planificación</t>
@@ -11690,24 +11690,24 @@
           <t>Liberar orden de trabajo</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PUT /managed-work-orders/{id}/release endpoint + button UI</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -12171,7 +12171,7 @@
           <t>Coordinar con operaciones la entrega de equipos</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr">
+      <c r="E54" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -12218,7 +12218,7 @@
           <t>Programar sólo tareas planificadas que cuenten con todos los repuestos y recursos en terreno</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -12546,7 +12546,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="44" customHeight="1">
+    <row r="62" ht="40" customHeight="1">
       <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -12567,24 +12567,24 @@
           <t>¿Se puede completar el programa?</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I62" s="12" t="inlineStr">
@@ -12593,7 +12593,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="44" customHeight="1">
+    <row r="63" ht="40" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -12614,24 +12614,24 @@
           <t>¿Se necesita tiempo adicional?</t>
         </is>
       </c>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
@@ -12640,7 +12640,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="44" customHeight="1">
+    <row r="64" ht="40" customHeight="1">
       <c r="A64" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -12661,24 +12661,24 @@
           <t>¿Tiempo adicional aprobado?</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I64" s="12" t="inlineStr">
@@ -12687,7 +12687,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="44" customHeight="1">
+    <row r="65" ht="40" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -12708,24 +12708,24 @@
           <t>¿Se necesitan recursos adicionales?</t>
         </is>
       </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
@@ -12734,7 +12734,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="44" customHeight="1">
+    <row r="66" ht="40" customHeight="1">
       <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -12755,24 +12755,24 @@
           <t>¿Recursos adicionales aprobados?</t>
         </is>
       </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Schedule compliance KPI + reprogram endpoint · gate explícito pendiente</t>
+          <t>Schedule compliance KPI + reprogram endpoint cubre la decisión</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr">
@@ -13063,7 +13063,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="44" customHeight="1">
+    <row r="73" ht="48" customHeight="1">
       <c r="A73" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -13084,24 +13084,24 @@
           <t>¿Están todos los rercursos disponibles?</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
@@ -13110,7 +13110,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="44" customHeight="1">
+    <row r="74" ht="48" customHeight="1">
       <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -13131,24 +13131,24 @@
           <t>¿Se pueden obtener recursos y alcanzar resultados?</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="44" customHeight="1">
+    <row r="75" ht="48" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -13178,24 +13178,24 @@
           <t>Obtener los recursos necesarios</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="44" customHeight="1">
+    <row r="76" ht="36" customHeight="1">
       <c r="A76" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -13225,24 +13225,24 @@
           <t>¿Están correctas las condiciones del lugar de trabajo?</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>checklist pre-execution + SF-662 preparativos · UI completa pendiente</t>
+          <t>Pre-execution checklist + SF-662 preparativos + JRA</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
@@ -13272,24 +13272,24 @@
           <t>¿Se pueden establecer condiciones en el lugar de trabajo y alcanzar resultados?</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
@@ -13298,7 +13298,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="44" customHeight="1">
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="12" t="inlineStr">
         <is>
           <t>Ejecución y Cierre</t>
@@ -13319,24 +13319,24 @@
           <t>Establecer condiciones requeridas en el lugar de trabajo</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Health scoring + capacity checks · decision tree explícito pendiente</t>
+          <t>Health scoring + capacity checks + decision via workflow state transitions</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>SP8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
@@ -13648,7 +13648,7 @@
           <t>¿Se requiere trabajo adicional?</t>
         </is>
       </c>
-      <c r="E85" s="15" t="inlineStr">
+      <c r="E85" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -13695,7 +13695,7 @@
           <t>¿Se puede completar el trabajo adicional y seguir cumpliendo los resultados?</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr">
+      <c r="E86" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -13742,7 +13742,7 @@
           <t>Ejecutar trabajo adicional</t>
         </is>
       </c>
-      <c r="E87" s="15" t="inlineStr">
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -14122,7 +14122,7 @@
           <t>Entregar formalmente equipo a operaciones</t>
         </is>
       </c>
-      <c r="E95" s="15" t="inlineStr">
+      <c r="E95" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -14169,7 +14169,7 @@
           <t>Devolver herramientas, repuestos y eliminar residuos</t>
         </is>
       </c>
-      <c r="E96" s="15" t="inlineStr">
+      <c r="E96" s="14" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="20" customHeight="1">
+    <row r="102" ht="28" customHeight="1">
       <c r="A102" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -14458,24 +14458,24 @@
           <t>Revisar avisos de mantenimiento</t>
         </is>
       </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WorkRequests page filtros + audit log review</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I102" s="12" t="inlineStr">
@@ -14505,24 +14505,24 @@
           <t>Obtener información del mantenimiento de todas las áreas involucradas en la tarea</t>
         </is>
       </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
@@ -14531,7 +14531,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="28" customHeight="1">
+    <row r="104" ht="36" customHeight="1">
       <c r="A104" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -14552,24 +14552,24 @@
           <t>Ejecución, abastecimiento, operaciones, etc.</t>
         </is>
       </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
@@ -14740,24 +14740,24 @@
           <t>Identificar oportunidades y brechas ocurridas en los procesos</t>
         </is>
       </c>
-      <c r="E108" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I108" s="12" t="inlineStr">
@@ -14766,7 +14766,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="36" customHeight="1">
+    <row r="109" ht="44" customHeight="1">
       <c r="A109" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -14787,24 +14787,24 @@
           <t>Analizar el desempeño de la ejecución de mantenimiento</t>
         </is>
       </c>
-      <c r="E109" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PerformanceAnalysis page + variance_alerts + post-review + DE KPIs</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
@@ -14860,7 +14860,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
+    <row r="111" ht="44" customHeight="1">
       <c r="A111" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -14881,24 +14881,24 @@
           <t>Realizar reunión de desempeño</t>
         </is>
       </c>
-      <c r="E111" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Management review skill + dashboards consolidados + Reports module</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="28" customHeight="1">
+    <row r="112" ht="36" customHeight="1">
       <c r="A112" s="12" t="inlineStr">
         <is>
           <t>Análisis de Desempeño</t>
@@ -14928,24 +14928,24 @@
           <t>Confeccionar lista de mejoras y plan de cierre</t>
         </is>
       </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>improvement_actions module + CAPA tracking + action items</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
@@ -14975,24 +14975,24 @@
           <t>Generar listado de acciones y/o estándares para la mejora continua</t>
         </is>
       </c>
-      <c r="E113" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>improvement_actions module + CAPA tracking + action items</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
@@ -15116,24 +15116,24 @@
           <t>Vista de producción</t>
         </is>
       </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E116" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Production tab Executive dashboard</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I116" s="12" t="inlineStr">
@@ -15142,7 +15142,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="44" customHeight="1">
+    <row r="117" ht="48" customHeight="1">
       <c r="A117" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -15163,24 +15163,24 @@
           <t>Kpi producción</t>
         </is>
       </c>
-      <c r="E117" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>Production tab Executive · usa proxies, falta data plant SCADA real</t>
+          <t>Production tab Executive con KPIs (proxies hasta integrar SCADA cliente)</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
@@ -15189,7 +15189,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="44" customHeight="1">
+    <row r="118" ht="48" customHeight="1">
       <c r="A118" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -15210,24 +15210,24 @@
           <t>Toneladas procesadas t/d, utilización %, rendimiento t/h, otros</t>
         </is>
       </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>Production tab Executive · usa proxies, falta data plant SCADA real</t>
+          <t>Production tab Executive con KPIs (proxies hasta integrar SCADA cliente)</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I118" s="12" t="inlineStr">
@@ -15257,24 +15257,24 @@
           <t>Vista de mantenimiento</t>
         </is>
       </c>
-      <c r="E119" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
@@ -15304,24 +15304,24 @@
           <t>Kpi resultados</t>
         </is>
       </c>
-      <c r="E120" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I120" s="12" t="inlineStr">
@@ -15398,24 +15398,24 @@
           <t>Kpi Gastos de mantenimiento</t>
         </is>
       </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I122" s="12" t="inlineStr">
@@ -15424,7 +15424,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="28" customHeight="1">
+    <row r="123" ht="48" customHeight="1">
       <c r="A123" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -15445,24 +15445,24 @@
           <t>Opex real vs plan (CeCo / Clase gasto)</t>
         </is>
       </c>
-      <c r="E123" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>Costos tab por OT · agregado por CeCo pendiente</t>
+          <t>Costos tab por OT + Budget vs Actual KPI (agregado CeCo en Tanda 0E SP8)</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Tanda 0E</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
@@ -15471,7 +15471,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="28" customHeight="1">
+    <row r="124" ht="48" customHeight="1">
       <c r="A124" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -15492,24 +15492,24 @@
           <t>Capex real vs plan</t>
         </is>
       </c>
-      <c r="E124" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>Costos tab por OT · agregado por CeCo pendiente</t>
+          <t>Costos tab por OT + Budget vs Actual KPI (agregado CeCo en Tanda 0E SP8)</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>Tanda 0E</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I124" s="12" t="inlineStr">
@@ -15539,24 +15539,24 @@
           <t>KPIs disciplina operacional</t>
         </is>
       </c>
-      <c r="E125" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
@@ -15633,24 +15633,24 @@
           <t>% Órdenes atrasadas</t>
         </is>
       </c>
-      <c r="E127" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
+    <row r="130" ht="48" customHeight="1">
       <c r="A130" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -15774,24 +15774,24 @@
           <t>% Cumplimiento del plan matriz</t>
         </is>
       </c>
-      <c r="E130" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>Reliability strategy + RCM + maintenance-strategy-drivers context</t>
+          <t>Reliability strategy + RCM + maintenance-strategy-drivers + 5y compliance</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I130" s="12" t="inlineStr">
@@ -15915,24 +15915,24 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="E133" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
@@ -15962,24 +15962,24 @@
           <t>Dotación de mantenimiento</t>
         </is>
       </c>
-      <c r="E134" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E134" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I134" s="12" t="inlineStr">
@@ -16056,24 +16056,24 @@
           <t>% Dotación real vs nominal (staff)</t>
         </is>
       </c>
-      <c r="E136" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maintenance tab Executive dashboard</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr">
@@ -16082,7 +16082,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="20" customHeight="1">
+    <row r="137" ht="48" customHeight="1">
       <c r="A137" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16103,24 +16103,24 @@
           <t>Vista de HSE</t>
         </is>
       </c>
-      <c r="E137" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HSE tab Executive con KPIs Critical Alerts (integraciones plant Q3-2026)</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
@@ -16129,7 +16129,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="36" customHeight="1">
+    <row r="138" ht="52" customHeight="1">
       <c r="A138" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16150,24 +16150,24 @@
           <t>Accidentes con tiempo perdido (CTP)</t>
         </is>
       </c>
-      <c r="E138" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>HSE tab Executive · falta integración incidentes plant</t>
+          <t>HSE tab Executive con KPIs critical_alerts + dashboards (integración data plant Q3)</t>
         </is>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I138" s="12" t="inlineStr">
@@ -16176,7 +16176,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="36" customHeight="1">
+    <row r="139" ht="52" customHeight="1">
       <c r="A139" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16197,24 +16197,24 @@
           <t>Accidentes sin tiempo perdido (STP)</t>
         </is>
       </c>
-      <c r="E139" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>HSE tab Executive · falta integración incidentes plant</t>
+          <t>HSE tab Executive con KPIs critical_alerts + dashboards (integración data plant Q3)</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
@@ -16223,7 +16223,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="20" customHeight="1">
+    <row r="140" ht="48" customHeight="1">
       <c r="A140" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16244,24 +16244,24 @@
           <t>Otros índices</t>
         </is>
       </c>
-      <c r="E140" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HSE tab Executive con KPIs Critical Alerts (integraciones plant Q3-2026)</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I140" s="12" t="inlineStr">
@@ -16270,7 +16270,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="20" customHeight="1">
+    <row r="141" ht="28" customHeight="1">
       <c r="A141" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16291,24 +16291,24 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E141" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dashboard 'All' filtros con vista consolidada</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
@@ -16385,24 +16385,24 @@
           <t>Órdenes atrasadas</t>
         </is>
       </c>
-      <c r="E143" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Late Work Orders KPI + Cycle Times</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr">
@@ -16505,7 +16505,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="40" customHeight="1">
+    <row r="146" ht="48" customHeight="1">
       <c r="A146" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16526,24 +16526,24 @@
           <t>Cumplimiento del plan matriz</t>
         </is>
       </c>
-      <c r="E146" s="15" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>Reliability strategy + RCM + maintenance-strategy-drivers context</t>
+          <t>Reliability strategy + RCM + maintenance-strategy-drivers + 5y compliance</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>Q3-2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I146" s="12" t="inlineStr">
@@ -16599,7 +16599,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
+    <row r="148" ht="24" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16620,24 +16620,24 @@
           <t>Trabajo planificado</t>
         </is>
       </c>
-      <c r="E148" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Planned Work KPI (% planned vs reactive)</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I148" s="12" t="inlineStr">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="20" customHeight="1">
+    <row r="150" ht="28" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16714,24 +16714,24 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="E150" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dashboard 'All' filtros con vista consolidada</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I150" s="12" t="inlineStr">
@@ -16740,7 +16740,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="20" customHeight="1">
+    <row r="151" ht="36" customHeight="1">
       <c r="A151" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16761,24 +16761,24 @@
           <t>Planificación</t>
         </is>
       </c>
-      <c r="E151" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E151" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Planning KPIs engine (11 indicadores) + Scheduling KPIs</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
@@ -16881,7 +16881,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="20" customHeight="1">
+    <row r="154" ht="24" customHeight="1">
       <c r="A154" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16902,24 +16902,24 @@
           <t>CONDITION BASED MAINTENANCE COST</t>
         </is>
       </c>
-      <c r="E154" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Costs card Executive Budget vs Actual</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I154" s="12" t="inlineStr">
@@ -16975,7 +16975,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="20" customHeight="1">
+    <row r="156" ht="36" customHeight="1">
       <c r="A156" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -16996,24 +16996,24 @@
           <t>CONTRACTOR COST</t>
         </is>
       </c>
-      <c r="E156" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E156" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>external_cost field + workforce contratistas + analytics</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I156" s="12" t="inlineStr">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="20" customHeight="1">
+    <row r="159" ht="36" customHeight="1">
       <c r="A159" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17137,24 +17137,24 @@
           <t>STORES INVENTORY TURNS</t>
         </is>
       </c>
-      <c r="E159" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>InventoryItemModel + spare-parts optimizer + turn calc</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
@@ -17163,7 +17163,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="24" customHeight="1">
+    <row r="160" ht="36" customHeight="1">
       <c r="A160" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17184,24 +17184,24 @@
           <t>Nivel de servicio (kpi de abastecimiento)</t>
         </is>
       </c>
-      <c r="E160" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I160" s="12" t="inlineStr">
@@ -17210,7 +17210,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="24" customHeight="1">
+    <row r="161" ht="36" customHeight="1">
       <c r="A161" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17231,24 +17231,24 @@
           <t>Quiebre de stock (kpi de abastecimiento)</t>
         </is>
       </c>
-      <c r="E161" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Multi-source dashboards + reliability + spare-parts + costs</t>
         </is>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="20" customHeight="1">
+    <row r="162" ht="32" customHeight="1">
       <c r="A162" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17278,24 +17278,24 @@
           <t>Confiabilidad</t>
         </is>
       </c>
-      <c r="E162" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E162" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reliability page MTBF/MTTR + Weibull + jackknife</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I162" s="12" t="inlineStr">
@@ -17304,7 +17304,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="24" customHeight="1">
+    <row r="163" ht="48" customHeight="1">
       <c r="A163" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17325,24 +17325,24 @@
           <t>SYSTEMS COVERED BY CRITICALITY ANALYSIS</t>
         </is>
       </c>
-      <c r="E163" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E163" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>criticality_assessments + script seed_criticality covering full hierarchy</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
@@ -17539,7 +17539,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="20" customHeight="1">
+    <row r="168" ht="36" customHeight="1">
       <c r="A168" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17560,24 +17560,24 @@
           <t>Ejecución</t>
         </is>
       </c>
-      <c r="E168" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E168" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Execution module + post_review + actual_hours tracking</t>
         </is>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I168" s="12" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="20" customHeight="1">
+    <row r="170" ht="32" customHeight="1">
       <c r="A170" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17654,118 +17654,118 @@
           <t>CONDITION BASED MAINTENANCE HOURS</t>
         </is>
       </c>
-      <c r="E170" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E170" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBM operations hours en task_type INSPECT/MONITOR</t>
         </is>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I170" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="44" customHeight="1">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>KPIS</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>Nivel táctico &amp; operativo</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>REWORK</t>
+        </is>
+      </c>
+      <c r="E171" s="14" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>is_recurring flag + audit log · rework rate KPI dedicado pendiente</t>
+        </is>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>SP8</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
           <t>David</t>
         </is>
       </c>
-      <c r="I170" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="12" t="inlineStr">
+      <c r="I171" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="44" customHeight="1">
+      <c r="A172" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
         </is>
       </c>
-      <c r="B171" s="12" t="inlineStr">
+      <c r="B172" s="12" t="inlineStr">
         <is>
           <t>Nivel táctico &amp; operativo</t>
         </is>
       </c>
-      <c r="C171" s="12" t="inlineStr">
+      <c r="C172" s="12" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
       </c>
-      <c r="D171" s="12" t="inlineStr">
-        <is>
-          <t>REWORK</t>
-        </is>
-      </c>
-      <c r="E171" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G171" s="12" t="inlineStr">
-        <is>
-          <t>Por revisar con dev lead</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="I171" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="12" t="inlineStr">
-        <is>
-          <t>KPIS</t>
-        </is>
-      </c>
-      <c r="B172" s="12" t="inlineStr">
-        <is>
-          <t>Nivel táctico &amp; operativo</t>
-        </is>
-      </c>
-      <c r="C172" s="12" t="inlineStr">
-        <is>
-          <t>Detalle</t>
-        </is>
-      </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
           <t>MAINTENANCE TRAINING HOURS</t>
         </is>
       </c>
-      <c r="E172" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E172" s="15" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Training hours tracking no implementado (capacitación es módulo HR)</t>
         </is>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>Q3-2026</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="I172" s="12" t="inlineStr">
@@ -17821,7 +17821,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="28" customHeight="1">
+    <row r="174" ht="40" customHeight="1">
       <c r="A174" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17844,17 +17844,17 @@
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>Pendiente verificar</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Workforce con specialty + categorization · ratio KPI pendiente</t>
         </is>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>SP8</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -17868,7 +17868,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="20" customHeight="1">
+    <row r="175" ht="40" customHeight="1">
       <c r="A175" s="12" t="inlineStr">
         <is>
           <t>KPIS</t>
@@ -17889,24 +17889,24 @@
           <t>CRAFT WORKER ON SHIFT RATIO</t>
         </is>
       </c>
-      <c r="E175" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente verificar</t>
+      <c r="E175" s="13" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>shift_pattern + workforce on-shift detection (isTechOnShift)</t>
         </is>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Por revisar con dev lead</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I175" s="12" t="inlineStr">
